--- a/data/baidu/china_children.xlsx
+++ b/data/baidu/china_children.xlsx
@@ -583,16 +583,24 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>天堂回信</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>天堂回信</t>
+        </is>
+      </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
@@ -657,24 +665,30 @@
           <t>https://movie.douban.com/subject/21359690/</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>1773.571428571429</v>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>熊出没之过年</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>熊出没之过年</t>
+        </is>
+      </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -734,24 +748,30 @@
           <t>https://movie.douban.com/subject/26787574/</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>5014</v>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>奇迹男孩</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>奇迹男孩</t>
+        </is>
+      </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -981,24 +1001,30 @@
           <t>https://movie.douban.com/subject/11502154/</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>750.5714285714286</v>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>邋遢大王奇遇记</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>邋遢大王奇遇记</t>
+        </is>
+      </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1058,24 +1084,30 @@
           <t>https://movie.douban.com/subject/10467774/</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>575.5714285714286</v>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>孙子从美国来</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>孙子从美国来</t>
+        </is>
+      </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1220,24 +1252,30 @@
           <t>https://movie.douban.com/subject/19976058/</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>35.57142857142857</v>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>念书的孩子</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>念书的孩子</t>
+        </is>
+      </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1297,24 +1335,30 @@
           <t>https://movie.douban.com/subject/4812830/</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>898.4285714285714</v>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>魁拔之十万火急</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>魁拔之十万火急</t>
+        </is>
+      </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -1374,24 +1418,30 @@
           <t>https://movie.douban.com/subject/26887890/</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>340</v>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>小戏骨：白蛇传</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>小戏骨</t>
+        </is>
+      </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1454,16 +1504,24 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>喜羊羊与灰太狼之虎虎生威</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>喜羊羊与灰太狼之虎虎生威</t>
+        </is>
+      </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
@@ -1613,24 +1671,30 @@
           <t>https://movie.douban.com/subject/11537965/</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>992.4285714285714</v>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>家在水草丰茂的地方</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>家在水草丰茂的地方</t>
+        </is>
+      </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -1690,24 +1754,30 @@
           <t>https://movie.douban.com/subject/30299040/</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>5504.857142857143</v>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>树上有个好地方</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>树上有个好地方</t>
+        </is>
+      </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1767,21 +1837,27 @@
           <t>https://movie.douban.com/subject/30206431/</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>过昭关</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>过昭关</t>
+        </is>
+      </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1932,16 +2008,24 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>走路上学</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>走路上学</t>
+        </is>
+      </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
@@ -2009,16 +2093,24 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>闪闪的红星</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>闪闪的红星</t>
+        </is>
+      </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
@@ -2171,16 +2263,24 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>电影往事</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>电影往事</t>
+        </is>
+      </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
@@ -2333,16 +2433,24 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>喜羊羊与灰太狼之牛气冲天</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>喜羊羊与灰太狼之牛气冲天</t>
+        </is>
+      </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
@@ -2407,24 +2515,30 @@
           <t>https://movie.douban.com/subject/26951953/</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>1123.142857142857</v>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>小戏骨：放开那三国</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>小戏骨</t>
+        </is>
+      </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -2487,16 +2601,24 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2675728828, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>树上有个好地方2：美术老师的放羊班</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>树上有个好地方2</t>
+        </is>
+      </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
@@ -2646,24 +2768,30 @@
           <t>https://movie.douban.com/subject/11537964/</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>58.71428571428572</v>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>有人赞美聪慧，有人则不</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>有人赞美聪慧，有人则不</t>
+        </is>
+      </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -2808,24 +2936,30 @@
           <t>https://movie.douban.com/subject/34889288/</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>290.8571428571428</v>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>流水落花</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>流水落花</t>
+        </is>
+      </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -2888,16 +3022,24 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2677086275, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>游泳回家</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>游泳回家</t>
+        </is>
+      </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
@@ -2962,24 +3104,30 @@
           <t>https://movie.douban.com/subject/35448988/</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>736</v>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>向着明亮那方</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>向着明亮那方</t>
+        </is>
+      </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -3042,16 +3190,24 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2677539311, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>矮婆</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>矮婆</t>
+        </is>
+      </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
@@ -3116,24 +3272,30 @@
           <t>https://movie.douban.com/subject/7056398/</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="n">
+        <v>98441.85714285714</v>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>喜羊羊与灰太狼之开心闯龙年</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>喜羊羊与灰太狼之开心闯龙年</t>
+        </is>
+      </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -3193,24 +3355,30 @@
           <t>https://movie.douban.com/subject/30337172/</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="n">
+        <v>3919.857142857143</v>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>第一次的离别</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>第一次的离别</t>
+        </is>
+      </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -3273,16 +3441,24 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>龙在少林</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>龙在少林</t>
+        </is>
+      </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
@@ -3347,24 +3523,30 @@
           <t>https://movie.douban.com/subject/25882279/</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
+      <c r="O37" t="n">
+        <v>3582.285714285714</v>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>有一天</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>有一天</t>
+        </is>
+      </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -3424,24 +3606,30 @@
           <t>https://movie.douban.com/subject/26841305/</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>51.14285714285715</v>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>那年八岁</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>那年八岁</t>
+        </is>
+      </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -3671,24 +3859,30 @@
           <t>https://movie.douban.com/subject/11615929/</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>413</v>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>我的影子在奔跑</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>我的影子在奔跑</t>
+        </is>
+      </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -3748,21 +3942,27 @@
           <t>https://movie.douban.com/subject/33427574/</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>天堂的张望</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>天堂的张望</t>
+        </is>
+      </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -3828,16 +4028,24 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2681716128, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>旺扎的雨靴</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>旺扎的雨靴</t>
+        </is>
+      </c>
       <c r="T43" t="n">
         <v>0</v>
       </c>
@@ -3898,24 +4106,30 @@
           <t>https://movie.douban.com/subject/27205168/</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
+      <c r="O44" t="n">
+        <v>73.71428571428571</v>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>留夏</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>留夏</t>
+        </is>
+      </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -4063,16 +4277,24 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>滚拉拉的枪</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>滚拉拉的枪</t>
+        </is>
+      </c>
       <c r="T46" t="n">
         <v>0</v>
       </c>
@@ -4218,24 +4440,30 @@
           <t>https://movie.douban.com/subject/35377026/</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>20154.42857142857</v>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>熊出没·重返地球</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>熊出没</t>
+        </is>
+      </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -4295,21 +4523,27 @@
           <t>https://movie.douban.com/subject/36404113/</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>河边有个好地方</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>河边有个好地方</t>
+        </is>
+      </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -4375,16 +4609,24 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>劳拉的星星</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>劳拉的星星</t>
+        </is>
+      </c>
       <c r="T50" t="n">
         <v>0</v>
       </c>
@@ -4704,21 +4946,27 @@
           <t>https://movie.douban.com/subject/25725249/</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>念书的孩子2</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>念书的孩子2</t>
+        </is>
+      </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -4951,24 +5199,30 @@
           <t>https://movie.douban.com/subject/10599639/</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
+      <c r="O57" t="n">
+        <v>6736.428571428572</v>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>猪猪侠之囧囧危机</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>猪猪侠之囧囧危机</t>
+        </is>
+      </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -5031,16 +5285,24 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>风筝</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>风筝</t>
+        </is>
+      </c>
       <c r="T58" t="n">
         <v>0</v>
       </c>
@@ -5105,24 +5367,30 @@
           <t>https://movie.douban.com/subject/26831711/</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
+      <c r="O59" t="n">
+        <v>132924.7142857143</v>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>熊出没·奇幻空间</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>熊出没</t>
+        </is>
+      </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -5182,24 +5450,30 @@
           <t>https://movie.douban.com/subject/26933248/</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>1510.857142857143</v>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>小戏骨：包青天之秦香莲与陈世美</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>小戏骨</t>
+        </is>
+      </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -5259,24 +5533,30 @@
           <t>https://movie.douban.com/subject/10569022/</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>5829.571428571428</v>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>愤怒的小孩</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>愤怒的小孩</t>
+        </is>
+      </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -5424,16 +5704,24 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2686874276, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>再见土拨鼠</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>再见土拨鼠</t>
+        </is>
+      </c>
       <c r="T63" t="n">
         <v>0</v>
       </c>
@@ -5583,24 +5871,30 @@
           <t>https://movie.douban.com/subject/25845586/</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
+      <c r="O65" t="n">
+        <v>1936.571428571429</v>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>赛尔号大电影4：圣魔之战</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>赛尔号大电影4</t>
+        </is>
+      </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -5833,16 +6127,24 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>浅蓝深蓝</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>浅蓝深蓝</t>
+        </is>
+      </c>
       <c r="T68" t="n">
         <v>0</v>
       </c>
@@ -5992,24 +6294,30 @@
           <t>https://movie.douban.com/subject/33973077/</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr"/>
+      <c r="O70" t="n">
+        <v>1301</v>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>皮皮鲁与鲁西西之罐头小人</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>皮皮鲁与鲁西西之罐头小人</t>
+        </is>
+      </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
@@ -6069,24 +6377,30 @@
           <t>https://movie.douban.com/subject/5997849/</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr"/>
+      <c r="O71" t="n">
+        <v>181.5714285714286</v>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>暑假作业</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>暑假作业</t>
+        </is>
+      </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
@@ -6146,24 +6460,30 @@
           <t>https://movie.douban.com/subject/23249761/</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr"/>
+      <c r="O72" t="n">
+        <v>665.8571428571429</v>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>赛尔号大电影3之战神联盟</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>赛尔号大电影3之战神联盟</t>
+        </is>
+      </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -6226,16 +6546,24 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2691297679, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>蜻蜓少年</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>蜻蜓少年</t>
+        </is>
+      </c>
       <c r="T73" t="n">
         <v>0</v>
       </c>
@@ -6303,16 +6631,24 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>买买提的2008</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>买买提的2008</t>
+        </is>
+      </c>
       <c r="T74" t="n">
         <v>0</v>
       </c>
@@ -6545,24 +6881,30 @@
           <t>https://movie.douban.com/subject/25785314/</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr"/>
+      <c r="O77" t="n">
+        <v>223277.8571428571</v>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>爸爸去哪儿</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>爸爸去哪儿</t>
+        </is>
+      </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
@@ -6625,16 +6967,24 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>红孩儿大话火焰山</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>红孩儿大话火焰山</t>
+        </is>
+      </c>
       <c r="T78" t="n">
         <v>0</v>
       </c>
@@ -6787,16 +7137,24 @@
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>环游地球八十天</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>环游地球八十天</t>
+        </is>
+      </c>
       <c r="T80" t="n">
         <v>0</v>
       </c>
@@ -6861,24 +7219,30 @@
           <t>https://movie.douban.com/subject/35470200/</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr"/>
+      <c r="O81" t="n">
+        <v>198.2857142857143</v>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>百川东到海</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>百川东到海</t>
+        </is>
+      </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
@@ -6941,16 +7305,24 @@
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2692249860, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>只有大海知道</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>只有大海知道</t>
+        </is>
+      </c>
       <c r="T82" t="n">
         <v>0</v>
       </c>
@@ -7100,24 +7472,30 @@
           <t>https://movie.douban.com/subject/35392460/</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr"/>
+      <c r="O84" t="n">
+        <v>3850.428571428572</v>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>萌鸡小队：萌闯新世界</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>萌鸡小队</t>
+        </is>
+      </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
@@ -7177,24 +7555,30 @@
           <t>https://movie.douban.com/subject/7055665/</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr"/>
+      <c r="O85" t="n">
+        <v>34.57142857142857</v>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>蓝学校</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>蓝学校</t>
+        </is>
+      </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -7254,21 +7638,27 @@
           <t>https://movie.douban.com/subject/34834554/</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr"/>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>点点星光</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>点点星光</t>
+        </is>
+      </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -7334,16 +7724,24 @@
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>一诺千金</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>一诺千金</t>
+        </is>
+      </c>
       <c r="T87" t="n">
         <v>0</v>
       </c>
@@ -7496,16 +7894,24 @@
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>无声的河</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>无声的河</t>
+        </is>
+      </c>
       <c r="T89" t="n">
         <v>0</v>
       </c>
@@ -7655,24 +8061,30 @@
           <t>https://movie.douban.com/subject/20388613/</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr"/>
+      <c r="O91" t="n">
+        <v>54.28571428571428</v>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>95分的烦恼</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>95分的烦恼</t>
+        </is>
+      </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
@@ -7735,16 +8147,24 @@
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2694678680, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>巧虎大飞船历险记</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>巧虎大飞船历险记</t>
+        </is>
+      </c>
       <c r="T92" t="n">
         <v>0</v>
       </c>
@@ -7979,21 +8399,27 @@
           <t>https://movie.douban.com/subject/36088962/</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr"/>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>黑鹰少年</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>黑鹰少年</t>
+        </is>
+      </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -8059,16 +8485,24 @@
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>闪闪的红星</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>闪闪的红星</t>
+        </is>
+      </c>
       <c r="T96" t="n">
         <v>0</v>
       </c>
@@ -8133,24 +8567,30 @@
           <t>https://movie.douban.com/subject/10727042/</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr"/>
+      <c r="O97" t="n">
+        <v>778.5714285714286</v>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>摩尔庄园2海妖宝藏</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>摩尔庄园2海妖宝藏</t>
+        </is>
+      </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98">
@@ -8210,24 +8650,30 @@
           <t>https://movie.douban.com/subject/26890949/</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr"/>
+      <c r="O98" t="n">
+        <v>276.8571428571428</v>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>小戏骨：补锅</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>小戏骨</t>
+        </is>
+      </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
@@ -8375,16 +8821,24 @@
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2697762287, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>少年与海</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>少年与海</t>
+        </is>
+      </c>
       <c r="T100" t="n">
         <v>0</v>
       </c>
@@ -8537,16 +8991,24 @@
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>后门</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>后门</t>
+        </is>
+      </c>
       <c r="T102" t="n">
         <v>0</v>
       </c>
@@ -8692,24 +9154,30 @@
           <t>https://movie.douban.com/subject/20416699/</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr"/>
+      <c r="O104" t="n">
+        <v>1263.714285714286</v>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>波鲁鲁冰雪大冒险</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>波鲁鲁冰雪大冒险</t>
+        </is>
+      </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U104" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
@@ -8772,16 +9240,24 @@
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2726940570, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>奔跑的少年</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>奔跑的少年</t>
+        </is>
+      </c>
       <c r="T105" t="n">
         <v>0</v>
       </c>
@@ -8846,24 +9322,30 @@
           <t>https://movie.douban.com/subject/26379074/</t>
         </is>
       </c>
-      <c r="O106" t="inlineStr"/>
+      <c r="O106" t="n">
+        <v>3767.428571428572</v>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>赛尔号大电影5：雷神崛起</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>赛尔号大电影5</t>
+        </is>
+      </c>
       <c r="T106" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U106" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
@@ -8923,24 +9405,30 @@
           <t>https://movie.douban.com/subject/26628256/</t>
         </is>
       </c>
-      <c r="O107" t="inlineStr"/>
+      <c r="O107" t="n">
+        <v>651.2857142857143</v>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>一个人的课堂</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>一个人的课堂</t>
+        </is>
+      </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108">
@@ -9003,16 +9491,24 @@
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2728913657, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>天真派：红楼梦之桃花诗社</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>天真派</t>
+        </is>
+      </c>
       <c r="T108" t="n">
         <v>0</v>
       </c>
@@ -9165,16 +9661,24 @@
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2729196130, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>新大头儿子和小头爸爸5：我的外星朋友</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>新大头儿子和小头爸爸5</t>
+        </is>
+      </c>
       <c r="T110" t="n">
         <v>0</v>
       </c>
@@ -9239,24 +9743,30 @@
           <t>https://movie.douban.com/subject/26891306/</t>
         </is>
       </c>
-      <c r="O111" t="inlineStr"/>
+      <c r="O111" t="n">
+        <v>328.8571428571428</v>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>小戏骨：白毛女</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>小戏骨</t>
+        </is>
+      </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U111" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112">
@@ -9316,21 +9826,27 @@
           <t>https://movie.douban.com/subject/27621546/</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr"/>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>小狗奶瓶</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>小狗奶瓶</t>
+        </is>
+      </c>
       <c r="T112" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -9478,21 +9994,27 @@
           <t>https://movie.douban.com/subject/35211536/</t>
         </is>
       </c>
-      <c r="O114" t="inlineStr"/>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr"/>
-      <c r="S114" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>父子变形记</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>父子变形记</t>
+        </is>
+      </c>
       <c r="T114" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -9640,24 +10162,30 @@
           <t>https://movie.douban.com/subject/10767851/</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr"/>
+      <c r="O116" t="n">
+        <v>35.14285714285715</v>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>我和我的伙伴</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>我和我的伙伴</t>
+        </is>
+      </c>
       <c r="T116" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U116" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117">
@@ -9717,24 +10245,30 @@
           <t>https://movie.douban.com/subject/30185523/</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr"/>
+      <c r="O117" t="n">
+        <v>567.1428571428571</v>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>小戏骨：黄飞鸿</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>小戏骨</t>
+        </is>
+      </c>
       <c r="T117" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U117" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118">
@@ -9797,16 +10331,24 @@
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2731973669, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>新大头儿子和小头爸爸之秘密计划</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>新大头儿子和小头爸爸之秘密计划</t>
+        </is>
+      </c>
       <c r="T118" t="n">
         <v>0</v>
       </c>
@@ -9874,16 +10416,24 @@
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2733392196, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>巧虎魔法岛历险记</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>巧虎魔法岛历险记</t>
+        </is>
+      </c>
       <c r="T119" t="n">
         <v>0</v>
       </c>
@@ -9951,16 +10501,24 @@
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>孩子那些事儿</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>孩子那些事儿</t>
+        </is>
+      </c>
       <c r="T120" t="n">
         <v>0</v>
       </c>
@@ -10025,24 +10583,30 @@
           <t>https://movie.douban.com/subject/26891314/</t>
         </is>
       </c>
-      <c r="O121" t="inlineStr"/>
+      <c r="O121" t="n">
+        <v>1423.857142857143</v>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>小戏骨：花木兰</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>小戏骨</t>
+        </is>
+      </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122">
@@ -10442,24 +11006,30 @@
           <t>https://movie.douban.com/subject/26890963/</t>
         </is>
       </c>
-      <c r="O126" t="inlineStr"/>
+      <c r="O126" t="n">
+        <v>248.7142857142857</v>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R126" t="inlineStr"/>
-      <c r="S126" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>小戏骨：三笑寻亲记</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>小戏骨</t>
+        </is>
+      </c>
       <c r="T126" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U126" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127">
@@ -10522,16 +11092,24 @@
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R127" t="inlineStr"/>
-      <c r="S127" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>寻找那达慕</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>寻找那达慕</t>
+        </is>
+      </c>
       <c r="T127" t="n">
         <v>0</v>
       </c>
@@ -10599,16 +11177,24 @@
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R128" t="inlineStr"/>
-      <c r="S128" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>王首先的夏天</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>王首先的夏天</t>
+        </is>
+      </c>
       <c r="T128" t="n">
         <v>0</v>
       </c>
@@ -10673,24 +11259,30 @@
           <t>https://movie.douban.com/subject/30263969/</t>
         </is>
       </c>
-      <c r="O129" t="inlineStr"/>
+      <c r="O129" t="n">
+        <v>1156</v>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R129" t="inlineStr"/>
-      <c r="S129" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>纯真年代</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>纯真年代</t>
+        </is>
+      </c>
       <c r="T129" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U129" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130">
@@ -10750,24 +11342,30 @@
           <t>https://movie.douban.com/subject/6733088/</t>
         </is>
       </c>
-      <c r="O130" t="inlineStr"/>
+      <c r="O130" t="n">
+        <v>142.7142857142857</v>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R130" t="inlineStr"/>
-      <c r="S130" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>坏孩子的秋天</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>坏孩子的秋天</t>
+        </is>
+      </c>
       <c r="T130" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U130" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131">
@@ -11000,16 +11598,24 @@
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>火星没事</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>火星没事</t>
+        </is>
+      </c>
       <c r="T133" t="n">
         <v>0</v>
       </c>
@@ -11753,16 +12359,24 @@
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr"/>
-      <c r="S142" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2734882085, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>赛尔号大电影7：疯狂机器城</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>赛尔号大电影7</t>
+        </is>
+      </c>
       <c r="T142" t="n">
         <v>0</v>
       </c>
@@ -12251,16 +12865,24 @@
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>月光少年</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>月光少年</t>
+        </is>
+      </c>
       <c r="T148" t="n">
         <v>0</v>
       </c>
@@ -12324,16 +12946,24 @@
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr"/>
-      <c r="S149" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2736298439, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>憨爸</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>憨爸</t>
+        </is>
+      </c>
       <c r="T149" t="n">
         <v>0</v>
       </c>
@@ -12398,24 +13028,30 @@
           <t>https://movie.douban.com/subject/25791073/</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr"/>
+      <c r="O150" t="n">
+        <v>2063.285714285714</v>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr"/>
-      <c r="S150" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>巴啦啦小魔仙之魔法的考验</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>巴啦啦小魔仙之魔法的考验</t>
+        </is>
+      </c>
       <c r="T150" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U150" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151">
@@ -12475,24 +13111,30 @@
           <t>https://movie.douban.com/subject/25951736/</t>
         </is>
       </c>
-      <c r="O151" t="inlineStr"/>
+      <c r="O151" t="n">
+        <v>4811.285714285715</v>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr"/>
-      <c r="S151" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>爸爸去哪儿2</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>爸爸去哪儿2</t>
+        </is>
+      </c>
       <c r="T151" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U151" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152">
@@ -12555,16 +13197,24 @@
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R152" t="inlineStr"/>
-      <c r="S152" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2737059929, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>新大头儿子和小头爸爸3：俄罗斯奇遇记</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>新大头儿子和小头爸爸3</t>
+        </is>
+      </c>
       <c r="T152" t="n">
         <v>0</v>
       </c>
@@ -12629,24 +13279,30 @@
           <t>https://movie.douban.com/subject/5384872/</t>
         </is>
       </c>
-      <c r="O153" t="inlineStr"/>
+      <c r="O153" t="n">
+        <v>1151.428571428571</v>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R153" t="inlineStr"/>
-      <c r="S153" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>老夫子之小水虎传奇</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>老夫子之小水虎传奇</t>
+        </is>
+      </c>
       <c r="T153" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U153" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154">
@@ -12876,24 +13532,30 @@
           <t>https://movie.douban.com/subject/35026731/</t>
         </is>
       </c>
-      <c r="O156" t="inlineStr"/>
+      <c r="O156" t="n">
+        <v>357</v>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>猪猪侠大电影·恐龙日记</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>猪猪侠大电影</t>
+        </is>
+      </c>
       <c r="T156" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U156" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157">
@@ -12953,24 +13615,30 @@
           <t>https://movie.douban.com/subject/26969037/</t>
         </is>
       </c>
-      <c r="O157" t="inlineStr"/>
+      <c r="O157" t="n">
+        <v>1248.285714285714</v>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R157" t="inlineStr"/>
-      <c r="S157" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>赛尔号大电影6：圣者无敌</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>赛尔号大电影6</t>
+        </is>
+      </c>
       <c r="T157" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U157" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158">
@@ -13033,16 +13701,24 @@
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>功夫小子</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>功夫小子</t>
+        </is>
+      </c>
       <c r="T158" t="n">
         <v>0</v>
       </c>
@@ -13110,16 +13786,24 @@
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R159" t="inlineStr"/>
-      <c r="S159" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2739322609, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>从哪来，到哪去</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>从哪来，到哪去</t>
+        </is>
+      </c>
       <c r="T159" t="n">
         <v>0</v>
       </c>
@@ -13187,16 +13871,24 @@
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>西游新传</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>西游新传</t>
+        </is>
+      </c>
       <c r="T160" t="n">
         <v>0</v>
       </c>
@@ -13346,21 +14038,27 @@
           <t>https://movie.douban.com/subject/27069788/</t>
         </is>
       </c>
-      <c r="O162" t="inlineStr"/>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R162" t="inlineStr"/>
-      <c r="S162" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>旋风女队</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>旋风女队</t>
+        </is>
+      </c>
       <c r="T162" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U162" t="n">
         <v>0</v>
@@ -13423,24 +14121,30 @@
           <t>https://movie.douban.com/subject/20369263/</t>
         </is>
       </c>
-      <c r="O163" t="inlineStr"/>
+      <c r="O163" t="n">
+        <v>3077.857142857143</v>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R163" t="inlineStr"/>
-      <c r="S163" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>巴啦啦小魔仙</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>巴啦啦小魔仙</t>
+        </is>
+      </c>
       <c r="T163" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U163" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164">
@@ -13670,21 +14374,27 @@
           <t>https://movie.douban.com/subject/37006326/</t>
         </is>
       </c>
-      <c r="O166" t="inlineStr"/>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R166" t="inlineStr"/>
-      <c r="S166" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>奇妙萌可大电影</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>奇妙萌可大电影</t>
+        </is>
+      </c>
       <c r="T166" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U166" t="n">
         <v>0</v>
@@ -13747,24 +14457,30 @@
           <t>https://movie.douban.com/subject/26318077/</t>
         </is>
       </c>
-      <c r="O167" t="inlineStr"/>
+      <c r="O167" t="n">
+        <v>34708.14285714286</v>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R167" t="inlineStr"/>
-      <c r="S167" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>奥拉星：进击圣殿</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>奥拉星</t>
+        </is>
+      </c>
       <c r="T167" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U167" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168">
@@ -13827,16 +14543,24 @@
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R168" t="inlineStr"/>
-      <c r="S168" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>神秘谷</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>神秘谷</t>
+        </is>
+      </c>
       <c r="T168" t="n">
         <v>0</v>
       </c>
@@ -13901,24 +14625,30 @@
           <t>https://movie.douban.com/subject/26268610/</t>
         </is>
       </c>
-      <c r="O169" t="inlineStr"/>
+      <c r="O169" t="n">
+        <v>1235</v>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R169" t="inlineStr"/>
-      <c r="S169" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>我爸比我小四岁</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>我爸比我小四岁</t>
+        </is>
+      </c>
       <c r="T169" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U169" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170">
@@ -13977,16 +14707,24 @@
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R170" t="inlineStr"/>
-      <c r="S170" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>潜艇总动员</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>潜艇总动员</t>
+        </is>
+      </c>
       <c r="T170" t="n">
         <v>0</v>
       </c>
@@ -14051,24 +14789,30 @@
           <t>https://movie.douban.com/subject/27173314/</t>
         </is>
       </c>
-      <c r="O171" t="inlineStr"/>
+      <c r="O171" t="n">
+        <v>257.8571428571428</v>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr"/>
-      <c r="S171" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>小小爸爸</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>小小爸爸</t>
+        </is>
+      </c>
       <c r="T171" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U171" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172">
@@ -14216,16 +14960,24 @@
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R173" t="inlineStr"/>
-      <c r="S173" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2745875960, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>喜禾</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>喜禾</t>
+        </is>
+      </c>
       <c r="T173" t="n">
         <v>0</v>
       </c>
@@ -14290,21 +15042,27 @@
           <t>https://movie.douban.com/subject/34436818/</t>
         </is>
       </c>
-      <c r="O174" t="inlineStr"/>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr"/>
-      <c r="S174" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>来自汪星的你</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>来自汪星的你</t>
+        </is>
+      </c>
       <c r="T174" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U174" t="n">
         <v>0</v>
@@ -14452,24 +15210,30 @@
           <t>https://movie.douban.com/subject/26747836/</t>
         </is>
       </c>
-      <c r="O176" t="inlineStr"/>
+      <c r="O176" t="n">
+        <v>3092.714285714286</v>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R176" t="inlineStr"/>
-      <c r="S176" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>喵星人</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>喵星人</t>
+        </is>
+      </c>
       <c r="T176" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U176" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177">
@@ -14529,24 +15293,30 @@
           <t>https://movie.douban.com/subject/19977815/</t>
         </is>
       </c>
-      <c r="O177" t="inlineStr"/>
+      <c r="O177" t="n">
+        <v>1259</v>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R177" t="inlineStr"/>
-      <c r="S177" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>小小飞虎队</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>小小飞虎队</t>
+        </is>
+      </c>
       <c r="T177" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U177" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178">
@@ -14606,24 +15376,30 @@
           <t>https://movie.douban.com/subject/24325876/</t>
         </is>
       </c>
-      <c r="O178" t="inlineStr"/>
+      <c r="O178" t="n">
+        <v>1161</v>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R178" t="inlineStr"/>
-      <c r="S178" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>潜艇总动员3：彩虹宝藏</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>潜艇总动员3</t>
+        </is>
+      </c>
       <c r="T178" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U178" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="179">
@@ -14686,16 +15462,24 @@
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R179" t="inlineStr"/>
-      <c r="S179" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2749666677, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>大头儿子和小头爸爸之草原奇遇</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>大头儿子和小头爸爸之草原奇遇</t>
+        </is>
+      </c>
       <c r="T179" t="n">
         <v>0</v>
       </c>
@@ -14760,24 +15544,30 @@
           <t>https://movie.douban.com/subject/35168646/</t>
         </is>
       </c>
-      <c r="O180" t="inlineStr"/>
+      <c r="O180" t="n">
+        <v>6609.142857142857</v>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q180" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R180" t="inlineStr"/>
-      <c r="S180" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>外太空的莫扎特</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>外太空的莫扎特</t>
+        </is>
+      </c>
       <c r="T180" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U180" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="181">
@@ -14840,16 +15630,24 @@
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R181" t="inlineStr"/>
-      <c r="S181" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>虎王归来</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>虎王归来</t>
+        </is>
+      </c>
       <c r="T181" t="n">
         <v>0</v>
       </c>
@@ -14914,21 +15712,27 @@
           <t>https://movie.douban.com/subject/26754627/</t>
         </is>
       </c>
-      <c r="O182" t="inlineStr"/>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q182" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R182" t="inlineStr"/>
-      <c r="S182" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>山海经之小人国</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>山海经之小人国</t>
+        </is>
+      </c>
       <c r="T182" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U182" t="n">
         <v>0</v>
@@ -15076,24 +15880,30 @@
           <t>https://movie.douban.com/subject/25978333/</t>
         </is>
       </c>
-      <c r="O184" t="inlineStr"/>
+      <c r="O184" t="n">
+        <v>1396.285714285714</v>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R184" t="inlineStr"/>
-      <c r="S184" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>闯堂兔2疯狂马戏团</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>闯堂兔2疯狂马戏团</t>
+        </is>
+      </c>
       <c r="T184" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U184" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="185">
@@ -15156,16 +15966,24 @@
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R185" t="inlineStr"/>
-      <c r="S185" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>寻找成龙</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>寻找成龙</t>
+        </is>
+      </c>
       <c r="T185" t="n">
         <v>0</v>
       </c>
@@ -15233,16 +16051,24 @@
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R186" t="inlineStr"/>
-      <c r="S186" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2750675211, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>丑小鸭历险记</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>丑小鸭历险记</t>
+        </is>
+      </c>
       <c r="T186" t="n">
         <v>0</v>
       </c>
@@ -15310,16 +16136,24 @@
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R187" t="inlineStr"/>
-      <c r="S187" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2750888574, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>老师也疯狂</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>老师也疯狂</t>
+        </is>
+      </c>
       <c r="T187" t="n">
         <v>0</v>
       </c>
@@ -15384,24 +16218,30 @@
           <t>https://movie.douban.com/subject/25769893/</t>
         </is>
       </c>
-      <c r="O188" t="inlineStr"/>
+      <c r="O188" t="n">
+        <v>614.7142857142857</v>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q188" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R188" t="inlineStr"/>
-      <c r="S188" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>无敌小飞猪</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>无敌小飞猪</t>
+        </is>
+      </c>
       <c r="T188" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U188" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="189">
@@ -15461,24 +16301,30 @@
           <t>https://movie.douban.com/subject/30295908/</t>
         </is>
       </c>
-      <c r="O189" t="inlineStr"/>
+      <c r="O189" t="n">
+        <v>8504.714285714286</v>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q189" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R189" t="inlineStr"/>
-      <c r="S189" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>小猪佩奇过大年</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>小猪佩奇过大年</t>
+        </is>
+      </c>
       <c r="T189" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U189" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190">
@@ -15541,16 +16387,24 @@
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R190" t="inlineStr"/>
-      <c r="S190" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2753640034, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>西柏坡2：英雄王二小</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>西柏坡2</t>
+        </is>
+      </c>
       <c r="T190" t="n">
         <v>0</v>
       </c>
@@ -15615,24 +16469,30 @@
           <t>https://movie.douban.com/subject/4913184/</t>
         </is>
       </c>
-      <c r="O191" t="inlineStr"/>
+      <c r="O191" t="n">
+        <v>3492.571428571428</v>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q191" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R191" t="inlineStr"/>
-      <c r="S191" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>熊猫总动员</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>熊猫总动员</t>
+        </is>
+      </c>
       <c r="T191" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U191" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="192">
@@ -15692,24 +16552,30 @@
           <t>https://movie.douban.com/subject/6523584/</t>
         </is>
       </c>
-      <c r="O192" t="inlineStr"/>
+      <c r="O192" t="n">
+        <v>1074.285714285714</v>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q192" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R192" t="inlineStr"/>
-      <c r="S192" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>囧蛋奇兵</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>囧蛋奇兵</t>
+        </is>
+      </c>
       <c r="T192" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U192" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="193">
@@ -15772,16 +16638,24 @@
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R193" t="inlineStr"/>
-      <c r="S193" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2755659267, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>功夫四侠</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>功夫四侠</t>
+        </is>
+      </c>
       <c r="T193" t="n">
         <v>0</v>
       </c>
@@ -15846,24 +16720,30 @@
           <t>https://movie.douban.com/subject/26860477/</t>
         </is>
       </c>
-      <c r="O194" t="inlineStr"/>
+      <c r="O194" t="n">
+        <v>9196.857142857143</v>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q194" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R194" t="inlineStr"/>
-      <c r="S194" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>新东方神娃</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>新东方神娃</t>
+        </is>
+      </c>
       <c r="T194" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U194" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="195">
@@ -15926,16 +16806,24 @@
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R195" t="inlineStr"/>
-      <c r="S195" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2770079627, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>新地雷战：神勇小子</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>新地雷战</t>
+        </is>
+      </c>
       <c r="T195" t="n">
         <v>0</v>
       </c>
@@ -16003,16 +16891,24 @@
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R196" t="inlineStr"/>
-      <c r="S196" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2770273903, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>疯狂丑小鸭</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>疯狂丑小鸭</t>
+        </is>
+      </c>
       <c r="T196" t="n">
         <v>0</v>
       </c>
@@ -16080,16 +16976,24 @@
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R197" t="inlineStr"/>
-      <c r="S197" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2771678136, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>真假森林王</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>真假森林王</t>
+        </is>
+      </c>
       <c r="T197" t="n">
         <v>0</v>
       </c>
@@ -16154,24 +17058,30 @@
           <t>https://movie.douban.com/subject/24706750/</t>
         </is>
       </c>
-      <c r="O198" t="inlineStr"/>
+      <c r="O198" t="n">
+        <v>1482.571428571429</v>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R198" t="inlineStr"/>
-      <c r="S198" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>小神来了</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>小神来了</t>
+        </is>
+      </c>
       <c r="T198" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U198" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="199">
@@ -16234,16 +17144,24 @@
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R199" t="inlineStr"/>
-      <c r="S199" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2772188498, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>天边的孩子</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>天边的孩子</t>
+        </is>
+      </c>
       <c r="T199" t="n">
         <v>0</v>
       </c>
@@ -16311,16 +17229,24 @@
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R200" t="inlineStr"/>
-      <c r="S200" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2772386213, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>爸爸我来救你了</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>爸爸我来救你了</t>
+        </is>
+      </c>
       <c r="T200" t="n">
         <v>0</v>
       </c>
@@ -16385,24 +17311,30 @@
           <t>https://movie.douban.com/subject/21323597/</t>
         </is>
       </c>
-      <c r="O201" t="inlineStr"/>
+      <c r="O201" t="n">
+        <v>501.8571428571428</v>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q201" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R201" t="inlineStr"/>
-      <c r="S201" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>冲锋号</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>冲锋号</t>
+        </is>
+      </c>
       <c r="T201" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U201" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="202">
@@ -16462,24 +17394,30 @@
           <t>https://movie.douban.com/subject/26628447/</t>
         </is>
       </c>
-      <c r="O202" t="inlineStr"/>
+      <c r="O202" t="n">
+        <v>982.5714285714286</v>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q202" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R202" t="inlineStr"/>
-      <c r="S202" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>莫日根</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>莫日根</t>
+        </is>
+      </c>
       <c r="T202" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U202" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="203">
@@ -16539,24 +17477,30 @@
           <t>https://movie.douban.com/subject/20429112/</t>
         </is>
       </c>
-      <c r="O203" t="inlineStr"/>
+      <c r="O203" t="n">
+        <v>1869.142857142857</v>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q203" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R203" t="inlineStr"/>
-      <c r="S203" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>让熊猫飞</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>让熊猫飞</t>
+        </is>
+      </c>
       <c r="T203" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U203" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="204">
@@ -16619,16 +17563,24 @@
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R204" t="inlineStr"/>
-      <c r="S204" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2775319849, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>少年毛泽东</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>少年毛泽东</t>
+        </is>
+      </c>
       <c r="T204" t="n">
         <v>0</v>
       </c>
